--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.602268808893439</v>
+        <v>1.072868681445184</v>
       </c>
       <c r="D2" t="n">
-        <v>4.723038360846204</v>
+        <v>0.7674937336375083</v>
       </c>
       <c r="E2" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F2" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.77858789080363</v>
+        <v>1.91402053225559</v>
       </c>
       <c r="D3" t="n">
-        <v>15.24041260965728</v>
+        <v>2.476567049069307</v>
       </c>
       <c r="E3" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F3" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.71689668130638</v>
+        <v>3.691495710712287</v>
       </c>
       <c r="D4" t="n">
-        <v>19.40320107935951</v>
+        <v>3.153020175395921</v>
       </c>
       <c r="E4" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F4" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.37753645431228</v>
+        <v>5.261349673825745</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86264853923338</v>
+        <v>4.852680387625425</v>
       </c>
       <c r="E5" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F5" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.47178033055856</v>
+        <v>2.351664303715765</v>
       </c>
       <c r="D6" t="n">
-        <v>22.09436022271651</v>
+        <v>3.590333536191433</v>
       </c>
       <c r="E6" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F6" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.25481885946984</v>
+        <v>3.778908064663849</v>
       </c>
       <c r="D7" t="n">
-        <v>27.74868937296435</v>
+        <v>4.509162023106708</v>
       </c>
       <c r="E7" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F7" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.58677825366889</v>
+        <v>4.157851466221195</v>
       </c>
       <c r="D8" t="n">
-        <v>25.95826412480372</v>
+        <v>4.218217920280605</v>
       </c>
       <c r="E8" t="n">
-        <v>8.268439715788132</v>
+        <v>1.343621453815572</v>
       </c>
       <c r="F8" t="n">
-        <v>8.01767137678182</v>
+        <v>1.302871598727046</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
